--- a/business_forms/050_website_launch_checklist_form--business_forms.xlsx
+++ b/business_forms/050_website_launch_checklist_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description (2)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category (2)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description (3)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'business_forms',_'value':_'business_forms'}</t>
+          <t>business_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Business Forms', 'value': 'business_forms'}</t>
+          <t>Business Forms</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other_forms',_'value':_'other_forms'}</t>
+          <t>other_forms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other Forms', 'value': 'other_forms'}</t>
+          <t>Other Forms</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>Chatjimmy</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'another_tool',_'value':_'another_tool'}</t>
+          <t>another_tool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Another Tool', 'value': 'another_tool'}</t>
+          <t>Another Tool</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'050_website_launch_checklist_form--business_forms',_'value':_'050_website_launch_checklist_form--business_forms'}</t>
+          <t>050_website_launch_checklist_form--business_forms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '050_website_launch_checklist_form--business_forms', 'value': '050_website_launch_checklist_form--business_forms'}</t>
+          <t>050 website launch checklist form--business forms</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other_file',_'value':_'other_file'}</t>
+          <t>other_file</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other File', 'value': 'other_file'}</t>
+          <t>Other File</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'business_forms',_'value':_'business_forms'}</t>
+          <t>business_forms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Business Forms', 'value': 'business_forms'}</t>
+          <t>Business Forms</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
